--- a/research/traditional_assets/database/data/mexico/mexico_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06509999999999999</v>
+        <v>0.07625</v>
       </c>
       <c r="E2">
-        <v>-0.004500000000000004</v>
+        <v>0.034</v>
       </c>
       <c r="G2">
-        <v>0.1295010700909577</v>
+        <v>0.1478458656676478</v>
       </c>
       <c r="H2">
-        <v>0.1295010700909577</v>
+        <v>0.1478458656676478</v>
       </c>
       <c r="I2">
-        <v>0.1224043606206528</v>
+        <v>0.09976585496387477</v>
       </c>
       <c r="J2">
-        <v>0.1042043944978453</v>
+        <v>0.09465727714232033</v>
       </c>
       <c r="K2">
-        <v>160.321</v>
+        <v>101.63</v>
       </c>
       <c r="L2">
-        <v>0.1072237827715356</v>
+        <v>0.067989028632593</v>
       </c>
       <c r="M2">
-        <v>281.876</v>
+        <v>291.8</v>
       </c>
       <c r="N2">
-        <v>0.1186646459543656</v>
+        <v>0.1097776607351115</v>
       </c>
       <c r="O2">
-        <v>1.758197616032834</v>
+        <v>2.871199448981599</v>
       </c>
       <c r="P2">
-        <v>280.9</v>
+        <v>129.6</v>
       </c>
       <c r="Q2">
-        <v>0.1182537677864781</v>
+        <v>0.0487566306760468</v>
       </c>
       <c r="R2">
-        <v>1.752109829654256</v>
+        <v>1.275214011610745</v>
       </c>
       <c r="S2">
-        <v>0.9759999999999991</v>
+        <v>162.2</v>
       </c>
       <c r="T2">
-        <v>0.003462515432317754</v>
+        <v>0.5558601782042495</v>
       </c>
       <c r="U2">
-        <v>194.75</v>
+        <v>168.882</v>
       </c>
       <c r="V2">
-        <v>0.08198619179927591</v>
+        <v>0.06353485572401339</v>
       </c>
       <c r="W2">
-        <v>0.04897108622036989</v>
+        <v>0.20142089093702</v>
       </c>
       <c r="X2">
-        <v>0.05968091283799651</v>
+        <v>0.09211412636349045</v>
       </c>
       <c r="Y2">
-        <v>-0.01070982661762662</v>
+        <v>0.1093067645735296</v>
       </c>
       <c r="Z2">
-        <v>1.459089006185905</v>
+        <v>1.544117571103474</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>-7.423822714681442</v>
       </c>
       <c r="AB2">
-        <v>0.05505612987710033</v>
+        <v>0.09118381573431011</v>
       </c>
       <c r="AC2">
-        <v>-0.05505612987710033</v>
+        <v>-7.515052777437636</v>
       </c>
       <c r="AD2">
-        <v>382.6</v>
+        <v>322.17</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>382.6</v>
+        <v>322.17</v>
       </c>
       <c r="AG2">
-        <v>187.85</v>
+        <v>153.288</v>
       </c>
       <c r="AH2">
-        <v>0.138723712835388</v>
+        <v>0.1081009438742127</v>
       </c>
       <c r="AI2">
-        <v>0.3192057400300351</v>
+        <v>0.2890428042095441</v>
       </c>
       <c r="AJ2">
-        <v>0.0732858675509607</v>
+        <v>0.05452395756117619</v>
       </c>
       <c r="AK2">
-        <v>0.1871295512277731</v>
+        <v>0.1620846585910537</v>
       </c>
       <c r="AL2">
-        <v>15.639</v>
+        <v>14.4</v>
       </c>
       <c r="AM2">
-        <v>15.639</v>
+        <v>12.183</v>
       </c>
       <c r="AN2">
-        <v>1.904619673436878</v>
+        <v>1.802853945159485</v>
       </c>
       <c r="AO2">
-        <v>11.70273035360317</v>
+        <v>10.35625</v>
       </c>
       <c r="AP2">
-        <v>0.9351354042214257</v>
+        <v>0.8577951874650253</v>
       </c>
       <c r="AQ2">
-        <v>11.70273035360317</v>
+        <v>12.24082738241812</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="E3">
-        <v>0.137</v>
+        <v>0.034</v>
       </c>
       <c r="G3">
-        <v>0.1422550831792976</v>
+        <v>0.1574859260314972</v>
       </c>
       <c r="H3">
-        <v>0.1422550831792976</v>
+        <v>0.1574859260314972</v>
       </c>
       <c r="I3">
-        <v>0.1353789279112754</v>
+        <v>0.1103826694220765</v>
       </c>
       <c r="J3">
-        <v>0.09737422128974892</v>
+        <v>0.08212157462677892</v>
       </c>
       <c r="K3">
-        <v>142.2</v>
+        <v>104.9</v>
       </c>
       <c r="L3">
-        <v>0.1051386321626617</v>
+        <v>0.07475236941495048</v>
       </c>
       <c r="M3">
-        <v>122</v>
+        <v>129.6</v>
       </c>
       <c r="N3">
-        <v>0.112483865019362</v>
+        <v>0.1145888594164456</v>
       </c>
       <c r="O3">
-        <v>0.8579465541490858</v>
+        <v>1.235462345090562</v>
       </c>
       <c r="P3">
-        <v>122</v>
+        <v>129.6</v>
       </c>
       <c r="Q3">
-        <v>0.112483865019362</v>
+        <v>0.1145888594164456</v>
       </c>
       <c r="R3">
-        <v>0.8579465541490858</v>
+        <v>1.235462345090562</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>159.4</v>
+        <v>122.1</v>
       </c>
       <c r="V3">
-        <v>0.1469666236400516</v>
+        <v>0.1079575596816976</v>
       </c>
       <c r="W3">
-        <v>0.3061356297093649</v>
+        <v>0.20142089093702</v>
       </c>
       <c r="X3">
-        <v>0.05957047452355504</v>
+        <v>0.09795919324710156</v>
       </c>
       <c r="Y3">
-        <v>0.2465651551858098</v>
+        <v>0.1034616976899184</v>
       </c>
       <c r="Z3">
-        <v>3.105625717566016</v>
+        <v>2.653242578937417</v>
       </c>
       <c r="AA3">
-        <v>0.3024078858654085</v>
+        <v>0.2178884584491565</v>
       </c>
       <c r="AB3">
-        <v>0.05577764076316002</v>
+        <v>0.09161825171075559</v>
       </c>
       <c r="AC3">
-        <v>0.2466302451022485</v>
+        <v>0.1262702067384009</v>
       </c>
       <c r="AD3">
-        <v>167.5</v>
+        <v>210</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>167.5</v>
+        <v>210</v>
       </c>
       <c r="AG3">
-        <v>8.099999999999994</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.133775257567287</v>
+        <v>0.1565995525727069</v>
       </c>
       <c r="AI3">
-        <v>0.2433531890164173</v>
+        <v>0.2928870292887029</v>
       </c>
       <c r="AJ3">
-        <v>0.007412830603093251</v>
+        <v>0.07211420132906719</v>
       </c>
       <c r="AK3">
-        <v>0.0153148043108338</v>
+        <v>0.1477559253656077</v>
       </c>
       <c r="AL3">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="AM3">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="AN3">
-        <v>0.8383383383383383</v>
+        <v>1.175153889199776</v>
       </c>
       <c r="AO3">
-        <v>12.37162162162162</v>
+        <v>10.75694444444444</v>
       </c>
       <c r="AP3">
-        <v>0.04054054054054051</v>
+        <v>0.4918858421936206</v>
       </c>
       <c r="AQ3">
-        <v>12.37162162162162</v>
+        <v>10.75694444444444</v>
       </c>
     </row>
     <row r="4">
@@ -856,10 +856,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0516</v>
-      </c>
-      <c r="E4">
-        <v>-0.146</v>
+        <v>-0.0275</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -874,85 +871,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>18.8</v>
+        <v>-22.6</v>
       </c>
       <c r="L4">
-        <v>0.146417445482866</v>
+        <v>-0.2469945355191257</v>
       </c>
       <c r="M4">
-        <v>159.876</v>
+        <v>162.2</v>
       </c>
       <c r="N4">
-        <v>0.1255899450117832</v>
+        <v>0.1606417747845895</v>
       </c>
       <c r="O4">
-        <v>8.504042553191489</v>
+        <v>-7.176991150442477</v>
       </c>
       <c r="P4">
-        <v>158.9</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.1248232521602514</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>8.452127659574469</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0.9759999999999991</v>
+        <v>162.2</v>
       </c>
       <c r="T4">
-        <v>0.006104731166654151</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>33.1</v>
+        <v>45.1</v>
       </c>
       <c r="V4">
-        <v>0.02600157109190888</v>
+        <v>0.04466673269287907</v>
       </c>
       <c r="W4">
-        <v>0.04897108622036989</v>
+        <v>-0.08361080281169071</v>
       </c>
       <c r="X4">
-        <v>0.05968091283799651</v>
+        <v>0.09510351039841991</v>
       </c>
       <c r="Y4">
-        <v>-0.01070982661762662</v>
+        <v>-0.1787143132101106</v>
       </c>
       <c r="Z4">
-        <v>0.2312263641274987</v>
+        <v>0.2085232452142206</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05505612987710033</v>
+        <v>0.09118381573431011</v>
       </c>
       <c r="AC4">
-        <v>-0.05505612987710033</v>
+        <v>-0.09118381573431011</v>
       </c>
       <c r="AD4">
-        <v>201.6</v>
+        <v>108.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>201.6</v>
+        <v>108.8</v>
       </c>
       <c r="AG4">
-        <v>168.5</v>
+        <v>63.7</v>
       </c>
       <c r="AH4">
-        <v>0.1367150413671504</v>
+        <v>0.09727313366115332</v>
       </c>
       <c r="AI4">
-        <v>0.4272091544818817</v>
+        <v>0.2671249693100908</v>
       </c>
       <c r="AJ4">
-        <v>0.1168921262573708</v>
+        <v>0.05934414011552076</v>
       </c>
       <c r="AK4">
-        <v>0.3840018231540565</v>
+        <v>0.1758696852567642</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Procorp, S.A.B. de C.V. (BMV:PROCORP B)</t>
+          <t>LIV Capital Acquisition Corp. II (NasdaqGM:LIVB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,26 +974,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="G5">
-        <v>0.08601398601398601</v>
-      </c>
-      <c r="H5">
-        <v>0.08601398601398601</v>
-      </c>
-      <c r="I5">
-        <v>-0.005664335664335664</v>
-      </c>
-      <c r="J5">
-        <v>-0.005664335664335664</v>
-      </c>
       <c r="K5">
-        <v>-0.679</v>
-      </c>
-      <c r="L5">
-        <v>-0.04748251748251749</v>
+        <v>-1.97</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1020,73 +999,236 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2.25</v>
+        <v>0.004</v>
       </c>
       <c r="V5">
-        <v>0.1264044943820225</v>
+        <v>3.108003108003109e-05</v>
       </c>
       <c r="W5">
-        <v>-0.03143518518518518</v>
+        <v>-6.86411149825784</v>
       </c>
       <c r="X5">
-        <v>0.0765380750654423</v>
+        <v>0.09211412636349045</v>
       </c>
       <c r="Y5">
-        <v>-0.1079732602506275</v>
+        <v>-6.956225624621331</v>
       </c>
       <c r="Z5">
-        <v>0.4212200653922059</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>-0.002385931838934873</v>
+        <v>-7.423822714681442</v>
       </c>
       <c r="AB5">
-        <v>0.05467710506203938</v>
+        <v>0.09123006275619429</v>
       </c>
       <c r="AC5">
-        <v>-0.05706303690097425</v>
+        <v>-7.515052777437636</v>
       </c>
       <c r="AD5">
-        <v>13.5</v>
+        <v>3.37</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>3.37</v>
       </c>
       <c r="AG5">
-        <v>11.25</v>
+        <v>3.366</v>
       </c>
       <c r="AH5">
-        <v>0.4313099041533546</v>
+        <v>0.02551677140910124</v>
       </c>
       <c r="AI5">
-        <v>0.3515625</v>
+        <v>-1.511210762331839</v>
       </c>
       <c r="AJ5">
-        <v>0.387263339070568</v>
+        <v>0.02548725637181409</v>
       </c>
       <c r="AK5">
-        <v>0.3112033195020747</v>
+        <v>-1.506714413607878</v>
       </c>
       <c r="AL5">
-        <v>0.839</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.839</v>
-      </c>
-      <c r="AN5">
-        <v>12.5</v>
-      </c>
-      <c r="AO5">
-        <v>-0.0965435041716329</v>
-      </c>
-      <c r="AP5">
-        <v>10.41666666666667</v>
+        <v>-0.704</v>
       </c>
       <c r="AQ5">
-        <v>-0.0965435041716329</v>
+        <v>3.806818181818182</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APx Acquisition Corp. I (NasdaqGM:APXI)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K6">
+        <v>13.4</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0.528</v>
+      </c>
+      <c r="V6">
+        <v>0.002382671480144405</v>
+      </c>
+      <c r="X6">
+        <v>0.09115449731022837</v>
+      </c>
+      <c r="AB6">
+        <v>0.09115449731022837</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>-0.528</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>-0</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.002388362162553376</v>
+      </c>
+      <c r="AK6">
+        <v>0.3020594965675057</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>-0.723</v>
+      </c>
+      <c r="AQ6">
+        <v>2.876901798063624</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LatAmGrowth SPAC (NasdaqGM:LATG)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K7">
+        <v>7.9</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>-0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>1.15</v>
+      </c>
+      <c r="V7">
+        <v>0.006882106523040095</v>
+      </c>
+      <c r="X7">
+        <v>0.09115449731022837</v>
+      </c>
+      <c r="AB7">
+        <v>0.09115449731022837</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>-1.15</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>-0</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.00692979813196746</v>
+      </c>
+      <c r="AK7">
+        <v>0.155615696887686</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-0.79</v>
+      </c>
+      <c r="AQ7">
+        <v>1.278481012658228</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07625</v>
+        <v>0.099</v>
       </c>
       <c r="E2">
-        <v>0.034</v>
+        <v>0.02155</v>
       </c>
       <c r="G2">
-        <v>0.1478458656676478</v>
+        <v>0.1062706690409565</v>
       </c>
       <c r="H2">
-        <v>0.1478458656676478</v>
+        <v>0.1062706690409565</v>
       </c>
       <c r="I2">
-        <v>0.09976585496387477</v>
+        <v>0.1162744848639023</v>
       </c>
       <c r="J2">
-        <v>0.09465727714232033</v>
+        <v>0.1057270889128824</v>
       </c>
       <c r="K2">
-        <v>101.63</v>
+        <v>147.078</v>
       </c>
       <c r="L2">
-        <v>0.067989028632593</v>
+        <v>0.09353726787077078</v>
       </c>
       <c r="M2">
-        <v>291.8</v>
+        <v>338.748</v>
       </c>
       <c r="N2">
-        <v>0.1097776607351115</v>
+        <v>0.1102228874499723</v>
       </c>
       <c r="O2">
-        <v>2.871199448981599</v>
+        <v>2.303186064537185</v>
       </c>
       <c r="P2">
-        <v>129.6</v>
+        <v>109.214</v>
       </c>
       <c r="Q2">
-        <v>0.0487566306760468</v>
+        <v>0.03553639410405753</v>
       </c>
       <c r="R2">
-        <v>1.275214011610745</v>
+        <v>0.7425583703885015</v>
       </c>
       <c r="S2">
-        <v>162.2</v>
+        <v>229.534</v>
       </c>
       <c r="T2">
-        <v>0.5558601782042495</v>
+        <v>0.6775951444731777</v>
       </c>
       <c r="U2">
-        <v>168.882</v>
+        <v>144.108</v>
       </c>
       <c r="V2">
-        <v>0.06353485572401339</v>
+        <v>0.04689031334396251</v>
       </c>
       <c r="W2">
-        <v>0.20142089093702</v>
+        <v>0.02958904109589041</v>
       </c>
       <c r="X2">
-        <v>0.09211412636349045</v>
+        <v>0.0794946508502163</v>
       </c>
       <c r="Y2">
-        <v>0.1093067645735296</v>
+        <v>-0.04990560975432588</v>
       </c>
       <c r="Z2">
-        <v>1.544117571103474</v>
+        <v>1.774453467429232</v>
       </c>
       <c r="AA2">
-        <v>-7.423822714681442</v>
+        <v>-0.186881370955828</v>
       </c>
       <c r="AB2">
-        <v>0.09118381573431011</v>
+        <v>0.07655082591111813</v>
       </c>
       <c r="AC2">
-        <v>-7.515052777437636</v>
+        <v>-0.2634321968669461</v>
       </c>
       <c r="AD2">
-        <v>322.17</v>
+        <v>430.99</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>322.17</v>
+        <v>430.99</v>
       </c>
       <c r="AG2">
-        <v>153.288</v>
+        <v>286.882</v>
       </c>
       <c r="AH2">
-        <v>0.1081009438742127</v>
+        <v>0.1229892503188948</v>
       </c>
       <c r="AI2">
-        <v>0.2890428042095441</v>
+        <v>0.3040922881535314</v>
       </c>
       <c r="AJ2">
-        <v>0.05452395756117619</v>
+        <v>0.08537692303571651</v>
       </c>
       <c r="AK2">
-        <v>0.1620846585910537</v>
+        <v>0.2253250098963864</v>
       </c>
       <c r="AL2">
-        <v>14.4</v>
+        <v>27.493</v>
       </c>
       <c r="AM2">
-        <v>12.183</v>
+        <v>16.905</v>
       </c>
       <c r="AN2">
-        <v>1.802853945159485</v>
+        <v>2.052528812267835</v>
       </c>
       <c r="AO2">
-        <v>10.35625</v>
+        <v>6.650056377987124</v>
       </c>
       <c r="AP2">
-        <v>0.8577951874650253</v>
+        <v>1.366234879512335</v>
       </c>
       <c r="AQ2">
-        <v>12.24082738241812</v>
+        <v>10.81514344868382</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.18</v>
+        <v>0.099</v>
       </c>
       <c r="E3">
-        <v>0.034</v>
+        <v>0.0563</v>
       </c>
       <c r="G3">
-        <v>0.1574859260314972</v>
+        <v>0.1258616855681566</v>
       </c>
       <c r="H3">
-        <v>0.1574859260314972</v>
+        <v>0.1258616855681566</v>
       </c>
       <c r="I3">
-        <v>0.1103826694220765</v>
+        <v>0.1444666814913646</v>
       </c>
       <c r="J3">
-        <v>0.08212157462677892</v>
+        <v>0.106501295009729</v>
       </c>
       <c r="K3">
-        <v>104.9</v>
+        <v>139.7</v>
       </c>
       <c r="L3">
-        <v>0.07475236941495048</v>
+        <v>0.1035505151582537</v>
       </c>
       <c r="M3">
-        <v>129.6</v>
+        <v>109.2</v>
       </c>
       <c r="N3">
-        <v>0.1145888594164456</v>
+        <v>0.07358986454612844</v>
       </c>
       <c r="O3">
-        <v>1.235462345090562</v>
+        <v>0.7816750178954904</v>
       </c>
       <c r="P3">
-        <v>129.6</v>
+        <v>109.2</v>
       </c>
       <c r="Q3">
-        <v>0.1145888594164456</v>
+        <v>0.07358986454612844</v>
       </c>
       <c r="R3">
-        <v>1.235462345090562</v>
+        <v>0.7816750178954904</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>122.1</v>
+        <v>133.8</v>
       </c>
       <c r="V3">
-        <v>0.1079575596816976</v>
+        <v>0.09016780106476179</v>
       </c>
       <c r="W3">
-        <v>0.20142089093702</v>
+        <v>0.2755424063116371</v>
       </c>
       <c r="X3">
-        <v>0.09795919324710156</v>
+        <v>0.08121265580348189</v>
       </c>
       <c r="Y3">
-        <v>0.1034616976899184</v>
+        <v>0.1943297505081552</v>
       </c>
       <c r="Z3">
-        <v>2.653242578937417</v>
+        <v>2.808869456589631</v>
       </c>
       <c r="AA3">
-        <v>0.2178884584491565</v>
+        <v>0.2991482346400695</v>
       </c>
       <c r="AB3">
-        <v>0.09161825171075559</v>
+        <v>0.07681978055067128</v>
       </c>
       <c r="AC3">
-        <v>0.1262702067384009</v>
+        <v>0.2223284540893982</v>
       </c>
       <c r="AD3">
-        <v>210</v>
+        <v>262.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>210</v>
+        <v>262.5</v>
       </c>
       <c r="AG3">
-        <v>87.90000000000001</v>
+        <v>128.7</v>
       </c>
       <c r="AH3">
-        <v>0.1565995525727069</v>
+        <v>0.1503092075125973</v>
       </c>
       <c r="AI3">
-        <v>0.2928870292887029</v>
+        <v>0.2990089987470099</v>
       </c>
       <c r="AJ3">
-        <v>0.07211420132906719</v>
+        <v>0.07980900409276942</v>
       </c>
       <c r="AK3">
-        <v>0.1477559253656077</v>
+        <v>0.1729606235721005</v>
       </c>
       <c r="AL3">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="AM3">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="AN3">
-        <v>1.175153889199776</v>
+        <v>1.215277777777778</v>
       </c>
       <c r="AO3">
-        <v>10.75694444444444</v>
+        <v>8.77927927927928</v>
       </c>
       <c r="AP3">
-        <v>0.4918858421936206</v>
+        <v>0.5958333333333333</v>
       </c>
       <c r="AQ3">
-        <v>10.75694444444444</v>
+        <v>8.77927927927928</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0275</v>
+        <v>0.14</v>
+      </c>
+      <c r="E4">
+        <v>-0.0132</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,85 +874,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-22.6</v>
+        <v>24.5</v>
       </c>
       <c r="L4">
-        <v>-0.2469945355191257</v>
+        <v>0.1208682782437099</v>
       </c>
       <c r="M4">
-        <v>162.2</v>
+        <v>0.348</v>
       </c>
       <c r="N4">
-        <v>0.1606417747845895</v>
+        <v>0.0002489092339603748</v>
       </c>
       <c r="O4">
-        <v>-7.176991150442477</v>
+        <v>0.01420408163265306</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.014</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>1.00135898719691e-05</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.0005714285714285715</v>
       </c>
       <c r="S4">
-        <v>162.2</v>
+        <v>0.334</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.9597701149425287</v>
       </c>
       <c r="U4">
-        <v>45.1</v>
+        <v>8.17</v>
       </c>
       <c r="V4">
-        <v>0.04466673269287907</v>
+        <v>0.005843644946713397</v>
       </c>
       <c r="W4">
-        <v>-0.08361080281169071</v>
+        <v>0.08207705192629816</v>
       </c>
       <c r="X4">
-        <v>0.09510351039841991</v>
+        <v>0.0794946508502163</v>
       </c>
       <c r="Y4">
-        <v>-0.1787143132101106</v>
+        <v>0.002582401076081861</v>
       </c>
       <c r="Z4">
-        <v>0.2085232452142206</v>
+        <v>0.5596355604638321</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.09118381573431011</v>
+        <v>0.07612978358655938</v>
       </c>
       <c r="AC4">
-        <v>-0.09118381573431011</v>
+        <v>-0.07612978358655938</v>
       </c>
       <c r="AD4">
-        <v>108.8</v>
+        <v>156.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>108.8</v>
+        <v>156.4</v>
       </c>
       <c r="AG4">
-        <v>63.7</v>
+        <v>148.23</v>
       </c>
       <c r="AH4">
-        <v>0.09727313366115332</v>
+        <v>0.1006111289803795</v>
       </c>
       <c r="AI4">
-        <v>0.2671249693100908</v>
+        <v>0.3014649190439476</v>
       </c>
       <c r="AJ4">
-        <v>0.05934414011552076</v>
+        <v>0.09585922797850396</v>
       </c>
       <c r="AK4">
-        <v>0.1758696852567642</v>
+        <v>0.2902884671875918</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LIV Capital Acquisition Corp. II (NasdaqGM:LIVB)</t>
+          <t>Agrinam Acquisition Corporation (TSX:AGRI.U)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,16 +978,16 @@
         </is>
       </c>
       <c r="K5">
-        <v>-1.97</v>
+        <v>-20.5</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>117.9</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>1.813846153846154</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-5.751219512195123</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -996,67 +999,73 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>117.9</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
       </c>
       <c r="U5">
-        <v>0.004</v>
+        <v>0.216</v>
       </c>
       <c r="V5">
-        <v>3.108003108003109e-05</v>
+        <v>0.003323076923076923</v>
       </c>
       <c r="W5">
-        <v>-6.86411149825784</v>
+        <v>-1.413793103448276</v>
       </c>
       <c r="X5">
-        <v>0.09211412636349045</v>
+        <v>0.07670198751099536</v>
       </c>
       <c r="Y5">
-        <v>-6.956225624621331</v>
+        <v>-1.490495090959271</v>
       </c>
       <c r="Z5">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>-7.423822714681442</v>
+        <v>-0.186881370955828</v>
       </c>
       <c r="AB5">
-        <v>0.09123006275619429</v>
+        <v>0.07655082591111813</v>
       </c>
       <c r="AC5">
-        <v>-7.515052777437636</v>
+        <v>-0.2634321968669461</v>
       </c>
       <c r="AD5">
-        <v>3.37</v>
+        <v>0.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.37</v>
+        <v>0.4</v>
       </c>
       <c r="AG5">
-        <v>3.366</v>
+        <v>0.184</v>
       </c>
       <c r="AH5">
-        <v>0.02551677140910124</v>
+        <v>0.006116207951070336</v>
       </c>
       <c r="AI5">
-        <v>-1.511210762331839</v>
+        <v>-0.02684563758389262</v>
       </c>
       <c r="AJ5">
-        <v>0.02548725637181409</v>
+        <v>0.002822778595974473</v>
       </c>
       <c r="AK5">
-        <v>-1.506714413607878</v>
+        <v>-0.01217253241598307</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="AM5">
-        <v>-0.704</v>
+        <v>-1.69</v>
+      </c>
+      <c r="AO5">
+        <v>-0.5548245614035088</v>
       </c>
       <c r="AQ5">
-        <v>3.806818181818182</v>
+        <v>1.497041420118343</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APx Acquisition Corp. I (NasdaqGM:APXI)</t>
+          <t>Procorp, S.A.B. de C.V. (BMV:PROCORP B)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1075,8 +1084,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.08990000000000001</v>
+      </c>
+      <c r="G6">
+        <v>-0.1310679611650485</v>
+      </c>
+      <c r="H6">
+        <v>-0.1310679611650485</v>
+      </c>
+      <c r="I6">
+        <v>-0.3699029126213592</v>
+      </c>
+      <c r="J6">
+        <v>-0.3699029126213592</v>
+      </c>
       <c r="K6">
-        <v>13.4</v>
+        <v>0.648</v>
+      </c>
+      <c r="L6">
+        <v>0.03145631067961165</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1100,49 +1127,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.528</v>
+        <v>1.83</v>
       </c>
       <c r="V6">
-        <v>0.002382671480144405</v>
+        <v>0.137593984962406</v>
+      </c>
+      <c r="W6">
+        <v>0.02958904109589041</v>
       </c>
       <c r="X6">
-        <v>0.09115449731022837</v>
+        <v>0.09660089765306348</v>
+      </c>
+      <c r="Y6">
+        <v>-0.06701185655717307</v>
+      </c>
+      <c r="Z6">
+        <v>0.6845218315943379</v>
+      </c>
+      <c r="AA6">
+        <v>-0.2532066192596531</v>
       </c>
       <c r="AB6">
-        <v>0.09115449731022837</v>
+        <v>0.0747820784055358</v>
+      </c>
+      <c r="AC6">
+        <v>-0.3279886976651889</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="AG6">
-        <v>-0.528</v>
+        <v>8.27</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.4316239316239316</v>
       </c>
       <c r="AI6">
-        <v>-0</v>
+        <v>0.2637075718015666</v>
       </c>
       <c r="AJ6">
-        <v>-0.002388362162553376</v>
+        <v>0.3834028743625406</v>
       </c>
       <c r="AK6">
-        <v>0.3020594965675057</v>
+        <v>0.2267617219632575</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.675</v>
       </c>
       <c r="AM6">
-        <v>-0.723</v>
+        <v>0.647</v>
+      </c>
+      <c r="AN6">
+        <v>-1.677740863787375</v>
+      </c>
+      <c r="AO6">
+        <v>-11.28888888888889</v>
+      </c>
+      <c r="AP6">
+        <v>-1.37375415282392</v>
       </c>
       <c r="AQ6">
-        <v>2.876901798063624</v>
+        <v>-11.7774343122102</v>
       </c>
     </row>
     <row r="7">
@@ -1153,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LatAmGrowth SPAC (NasdaqGM:LATG)</t>
+          <t>APx Acquisition Corp. I (NasdaqGM:APXI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1162,16 +1213,16 @@
         </is>
       </c>
       <c r="K7">
-        <v>7.9</v>
+        <v>2.73</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>111.3</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.9849557522123894</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>40.76923076923077</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1183,52 +1234,64 @@
         <v>-0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>111.3</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>1.15</v>
+        <v>0.092</v>
       </c>
       <c r="V7">
-        <v>0.006882106523040095</v>
+        <v>0.0008141592920353982</v>
+      </c>
+      <c r="W7">
+        <v>-0.385049365303244</v>
       </c>
       <c r="X7">
-        <v>0.09115449731022837</v>
+        <v>0.07691113427722429</v>
+      </c>
+      <c r="Y7">
+        <v>-0.4619604995804683</v>
       </c>
       <c r="AB7">
-        <v>0.09115449731022837</v>
+        <v>0.07656529896288283</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG7">
-        <v>-1.15</v>
+        <v>1.498</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.013875556331268</v>
       </c>
       <c r="AI7">
-        <v>-0</v>
+        <v>-0.5678571428571429</v>
       </c>
       <c r="AJ7">
-        <v>-0.00692979813196746</v>
+        <v>0.01308319795978969</v>
       </c>
       <c r="AK7">
-        <v>0.155615696887686</v>
+        <v>-0.5179806362378977</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="AM7">
-        <v>-0.79</v>
+        <v>-4.252</v>
+      </c>
+      <c r="AO7">
+        <v>-33.10344827586206</v>
       </c>
       <c r="AQ7">
-        <v>1.278481012658228</v>
+        <v>0.451552210724365</v>
       </c>
     </row>
   </sheetData>
